--- a/zoomInfo_march2.xlsx
+++ b/zoomInfo_march2.xlsx
@@ -38,7 +38,7 @@
     <t>First Name</t>
   </si>
   <si>
-    <t>Middle Name</t>
+    <t>Therapy/Device</t>
   </si>
   <si>
     <t>Salutation</t>
@@ -546,8 +546,16 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1019,144 +1027,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
@@ -1698,230 +1712,236 @@
   <dimension ref="A1:BU4"/>
   <sheetFormatPr defaultColWidth="8.4375" defaultRowHeight="16.8" outlineLevelRow="3"/>
   <cols>
+    <col min="1" max="1" width="18.8125" customWidth="1"/>
     <col min="2" max="2" width="11.125" customWidth="1"/>
+    <col min="3" max="3" width="10.6875" customWidth="1"/>
+    <col min="4" max="4" width="15.125" customWidth="1"/>
+    <col min="9" max="9" width="13.25" customWidth="1"/>
     <col min="19" max="19" width="22" customWidth="1"/>
     <col min="20" max="20" width="54.0625" customWidth="1"/>
     <col min="21" max="21" width="53.125" customWidth="1"/>
+    <col min="22" max="22" width="9.875"/>
+    <col min="28" max="28" width="10.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:73">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:73">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BK1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BU1" s="2" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1935,13 +1955,14 @@
       <c r="C2" t="s">
         <v>74</v>
       </c>
+      <c r="D2"/>
       <c r="G2" t="s">
         <v>75</v>
       </c>
       <c r="H2" t="s">
         <v>76</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="3">
         <v>43419</v>
       </c>
       <c r="J2" t="s">
@@ -1965,10 +1986,10 @@
       <c r="T2" t="s">
         <v>82</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="U2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2" s="3">
         <v>45738</v>
       </c>
       <c r="W2" t="s">
@@ -2102,13 +2123,14 @@
       <c r="C3" t="s">
         <v>109</v>
       </c>
+      <c r="D3"/>
       <c r="G3" t="s">
         <v>110</v>
       </c>
       <c r="H3" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="3">
         <v>41944</v>
       </c>
       <c r="J3" t="s">
@@ -2141,7 +2163,7 @@
       <c r="U3" t="s">
         <v>116</v>
       </c>
-      <c r="V3" s="1">
+      <c r="V3" s="3">
         <v>44836</v>
       </c>
       <c r="AA3" t="s">
@@ -2228,7 +2250,7 @@
       <c r="BF3" t="s">
         <v>131</v>
       </c>
-      <c r="BG3" s="1">
+      <c r="BG3" s="3">
         <v>44664</v>
       </c>
       <c r="BH3">
@@ -2272,13 +2294,14 @@
       <c r="C4" t="s">
         <v>138</v>
       </c>
+      <c r="D4"/>
       <c r="G4" t="s">
         <v>139</v>
       </c>
       <c r="H4" t="s">
         <v>140</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="3">
         <v>42490</v>
       </c>
       <c r="J4" t="s">
@@ -2311,7 +2334,7 @@
       <c r="U4" t="s">
         <v>146</v>
       </c>
-      <c r="V4" s="1">
+      <c r="V4" s="3">
         <v>45437</v>
       </c>
       <c r="Y4" t="s">
@@ -2413,7 +2436,7 @@
       <c r="BF4" t="s">
         <v>131</v>
       </c>
-      <c r="BG4" s="1">
+      <c r="BG4" s="3">
         <v>45552</v>
       </c>
       <c r="BH4">
@@ -2425,7 +2448,7 @@
       <c r="BJ4" t="s">
         <v>164</v>
       </c>
-      <c r="BK4" s="1">
+      <c r="BK4" s="3">
         <v>44775</v>
       </c>
       <c r="BN4" t="s">
@@ -2437,7 +2460,7 @@
       <c r="BP4" t="s">
         <v>147</v>
       </c>
-      <c r="BQ4" s="3" t="s">
+      <c r="BQ4" s="5" t="s">
         <v>167</v>
       </c>
       <c r="BR4" t="s">
